--- a/crates/tpt-lattice-import-xlsx/tests/fixtures/sample.xlsx
+++ b/crates/tpt-lattice-import-xlsx/tests/fixtures/sample.xlsx
@@ -19,13 +19,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +54,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +460,41 @@
         <v>3.5</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3.14159</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>centered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>